--- a/2022 data/excel_outputs/348_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/348_boothwise_data.xlsx
@@ -14,11 +14,89 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="436">
   <si>
     <t>AC 348 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -643,7 +721,7 @@
     <t>P.V. BIRADAR R.N.-2</t>
   </si>
   <si>
-    <t>####0##0 ###### #### ##0 . 1</t>
+    <t>NAN</t>
   </si>
   <si>
     <t>P.V. NIYAUJ R.N. - 2</t>
@@ -1250,8 +1328,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1267,7 +1353,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1275,12 +1361,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1579,91 +1683,169 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="D2" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="E2" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="F2" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="G2" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="H2" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="I2" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="J2" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="K2" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="L2" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="M2" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="N2" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="O2" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="P2" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="Q2" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="R2" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="S2" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="T2" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="U2" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="V2" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="W2" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="X2" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="Y2" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="Z2" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="AA2" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -1671,7 +1853,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>1103</v>
@@ -1754,7 +1936,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>1093</v>
@@ -1837,7 +2019,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>932</v>
@@ -1920,7 +2102,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>962</v>
@@ -2003,7 +2185,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>810</v>
@@ -2086,7 +2268,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>939</v>
@@ -2169,7 +2351,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>755</v>
@@ -2252,7 +2434,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>1002</v>
@@ -2335,7 +2517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>700</v>
@@ -2418,7 +2600,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>483</v>
@@ -2501,7 +2683,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>1159</v>
@@ -2584,7 +2766,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C14">
         <v>698</v>
@@ -2667,7 +2849,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>916</v>
@@ -2750,7 +2932,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>964</v>
@@ -2833,7 +3015,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>725</v>
@@ -2916,7 +3098,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C18">
         <v>1009</v>
@@ -2999,7 +3181,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C19">
         <v>966</v>
@@ -3082,7 +3264,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C20">
         <v>488</v>
@@ -3165,7 +3347,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C21">
         <v>980</v>
@@ -3248,7 +3430,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C22">
         <v>851</v>
@@ -3331,7 +3513,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C23">
         <v>857</v>
@@ -3414,7 +3596,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C24">
         <v>908</v>
@@ -3497,7 +3679,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C25">
         <v>583</v>
@@ -3580,7 +3762,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C26">
         <v>1040</v>
@@ -3663,7 +3845,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C27">
         <v>970</v>
@@ -3746,7 +3928,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C28">
         <v>928</v>
@@ -3829,7 +4011,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C29">
         <v>907</v>
@@ -3912,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C30">
         <v>812</v>
@@ -3995,7 +4177,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C31">
         <v>810</v>
@@ -4078,7 +4260,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C32">
         <v>739</v>
@@ -4161,7 +4343,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C33">
         <v>738</v>
@@ -4244,7 +4426,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C34">
         <v>760</v>
@@ -4327,7 +4509,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C35">
         <v>901</v>
@@ -4410,7 +4592,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C36">
         <v>998</v>
@@ -4493,7 +4675,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C37">
         <v>656</v>
@@ -4576,7 +4758,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C38">
         <v>624</v>
@@ -4659,7 +4841,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C39">
         <v>549</v>
@@ -4742,7 +4924,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C40">
         <v>910</v>
@@ -4825,7 +5007,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C41">
         <v>1068</v>
@@ -4908,7 +5090,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C42">
         <v>881</v>
@@ -4991,7 +5173,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C43">
         <v>545</v>
@@ -5074,7 +5256,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C44">
         <v>600</v>
@@ -5157,7 +5339,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="C45">
         <v>743</v>
@@ -5240,7 +5422,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C46">
         <v>669</v>
@@ -5323,7 +5505,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C47">
         <v>1089</v>
@@ -5406,7 +5588,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C48">
         <v>1097</v>
@@ -5489,7 +5671,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C49">
         <v>685</v>
@@ -5572,7 +5754,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C50">
         <v>601</v>
@@ -5655,7 +5837,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C51">
         <v>696</v>
@@ -5738,7 +5920,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C52">
         <v>918</v>
@@ -5821,7 +6003,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="C53">
         <v>1130</v>
@@ -5904,7 +6086,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="C54">
         <v>545</v>
@@ -5987,7 +6169,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C55">
         <v>690</v>
@@ -6070,7 +6252,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C56">
         <v>813</v>
@@ -6153,7 +6335,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C57">
         <v>1030</v>
@@ -6236,7 +6418,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C58">
         <v>778</v>
@@ -6319,7 +6501,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="C59">
         <v>691</v>
@@ -6402,7 +6584,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C60">
         <v>695</v>
@@ -6485,7 +6667,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C61">
         <v>1125</v>
@@ -6568,7 +6750,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C62">
         <v>1024</v>
@@ -6651,7 +6833,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C63">
         <v>750</v>
@@ -6734,7 +6916,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="C64">
         <v>849</v>
@@ -6817,7 +6999,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C65">
         <v>801</v>
@@ -6900,7 +7082,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="C66">
         <v>758</v>
@@ -6983,7 +7165,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="C67">
         <v>1043</v>
@@ -7066,7 +7248,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C68">
         <v>854</v>
@@ -7149,7 +7331,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C69">
         <v>1044</v>
@@ -7232,7 +7414,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C70">
         <v>1064</v>
@@ -7315,7 +7497,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C71">
         <v>688</v>
@@ -7398,7 +7580,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C72">
         <v>877</v>
@@ -7481,7 +7663,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C73">
         <v>650</v>
@@ -7564,7 +7746,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C74">
         <v>570</v>
@@ -7647,7 +7829,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C75">
         <v>851</v>
@@ -7730,7 +7912,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C76">
         <v>1130</v>
@@ -7813,7 +7995,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="C77">
         <v>1158</v>
@@ -7896,7 +8078,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C78">
         <v>796</v>
@@ -7979,7 +8161,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C79">
         <v>662</v>
@@ -8062,7 +8244,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C80">
         <v>985</v>
@@ -8145,7 +8327,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C81">
         <v>965</v>
@@ -8228,7 +8410,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C82">
         <v>1058</v>
@@ -8311,7 +8493,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="C83">
         <v>750</v>
@@ -8394,7 +8576,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="C84">
         <v>746</v>
@@ -8477,7 +8659,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="C85">
         <v>745</v>
@@ -8560,7 +8742,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C86">
         <v>1117</v>
@@ -8643,7 +8825,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="C87">
         <v>1000</v>
@@ -8726,7 +8908,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="C88">
         <v>1158</v>
@@ -8809,7 +8991,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C89">
         <v>915</v>
@@ -8892,7 +9074,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="C90">
         <v>1028</v>
@@ -8975,7 +9157,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="C91">
         <v>771</v>
@@ -9058,7 +9240,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C92">
         <v>677</v>
@@ -9141,7 +9323,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="C93">
         <v>1009</v>
@@ -9224,7 +9406,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="C94">
         <v>780</v>
@@ -9307,7 +9489,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="C95">
         <v>740</v>
@@ -9390,7 +9572,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="C96">
         <v>597</v>
@@ -9473,7 +9655,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="C97">
         <v>605</v>
@@ -9556,7 +9738,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="C98">
         <v>520</v>
@@ -9639,7 +9821,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="C99">
         <v>707</v>
@@ -9722,7 +9904,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="C100">
         <v>627</v>
@@ -9805,7 +9987,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="C101">
         <v>602</v>
@@ -9888,7 +10070,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C102">
         <v>634</v>
@@ -9971,7 +10153,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C103">
         <v>651</v>
@@ -10054,7 +10236,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C104">
         <v>994</v>
@@ -10137,7 +10319,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="C105">
         <v>767</v>
@@ -10220,7 +10402,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="C106">
         <v>1155</v>
@@ -10303,7 +10485,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="C107">
         <v>903</v>
@@ -10386,7 +10568,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="C108">
         <v>848</v>
@@ -10469,7 +10651,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="C109">
         <v>902</v>
@@ -10552,7 +10734,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="C110">
         <v>742</v>
@@ -10635,7 +10817,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="C111">
         <v>688</v>
@@ -10718,7 +10900,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C112">
         <v>664</v>
@@ -10801,7 +10983,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="C113">
         <v>1195</v>
@@ -10884,7 +11066,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="C114">
         <v>1009</v>
@@ -10967,7 +11149,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C115">
         <v>1086</v>
@@ -11050,7 +11232,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="C116">
         <v>1110</v>
@@ -11133,7 +11315,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C117">
         <v>1080</v>
@@ -11216,7 +11398,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="C118">
         <v>688</v>
@@ -11299,7 +11481,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C119">
         <v>587</v>
@@ -11382,7 +11564,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C120">
         <v>757</v>
@@ -11465,7 +11647,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="C121">
         <v>851</v>
@@ -11548,7 +11730,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="C122">
         <v>625</v>
@@ -11631,7 +11813,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="C123">
         <v>645</v>
@@ -11714,7 +11896,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="C124">
         <v>655</v>
@@ -11797,7 +11979,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="C125">
         <v>546</v>
@@ -11880,7 +12062,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="C126">
         <v>1092</v>
@@ -11963,7 +12145,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="C127">
         <v>871</v>
@@ -12046,7 +12228,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="C128">
         <v>996</v>
@@ -12129,7 +12311,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="C129">
         <v>1020</v>
@@ -12212,7 +12394,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="C130">
         <v>775</v>
@@ -12295,7 +12477,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="C131">
         <v>780</v>
@@ -12378,7 +12560,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="C132">
         <v>735</v>
@@ -12461,7 +12643,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="C133">
         <v>918</v>
@@ -12544,7 +12726,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="C134">
         <v>849</v>
@@ -12627,7 +12809,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="C135">
         <v>1143</v>
@@ -12710,7 +12892,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="C136">
         <v>873</v>
@@ -12793,7 +12975,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C137">
         <v>973</v>
@@ -12876,7 +13058,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="C138">
         <v>886</v>
@@ -12959,7 +13141,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="C139">
         <v>1056</v>
@@ -13042,7 +13224,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C140">
         <v>1153</v>
@@ -13125,7 +13307,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="C141">
         <v>803</v>
@@ -13208,7 +13390,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C142">
         <v>848</v>
@@ -13291,7 +13473,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C143">
         <v>682</v>
@@ -13374,7 +13556,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C144">
         <v>663</v>
@@ -13457,7 +13639,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="C145">
         <v>753</v>
@@ -13540,7 +13722,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="C146">
         <v>698</v>
@@ -13623,7 +13805,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C147">
         <v>1035</v>
@@ -13706,7 +13888,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C148">
         <v>1032</v>
@@ -13789,7 +13971,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="C149">
         <v>898</v>
@@ -13872,7 +14054,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="C150">
         <v>909</v>
@@ -13955,7 +14137,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="C151">
         <v>986</v>
@@ -14038,7 +14220,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="C152">
         <v>978</v>
@@ -14121,7 +14303,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="C153">
         <v>1152</v>
@@ -14204,7 +14386,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="C154">
         <v>1048</v>
@@ -14287,7 +14469,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="C155">
         <v>1009</v>
@@ -14370,7 +14552,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="C156">
         <v>1015</v>
@@ -14453,7 +14635,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="C157">
         <v>1059</v>
@@ -14536,7 +14718,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="C158">
         <v>891</v>
@@ -14619,7 +14801,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="C159">
         <v>720</v>
@@ -14702,7 +14884,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C160">
         <v>664</v>
@@ -14785,7 +14967,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C161">
         <v>623</v>
@@ -14868,7 +15050,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="C162">
         <v>1106</v>
@@ -14951,7 +15133,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="C163">
         <v>792</v>
@@ -15034,7 +15216,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C164">
         <v>739</v>
@@ -15117,7 +15299,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="C165">
         <v>819</v>
@@ -15200,7 +15382,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="C166">
         <v>640</v>
@@ -15283,7 +15465,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="C167">
         <v>620</v>
@@ -15366,7 +15548,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="C168">
         <v>825</v>
@@ -15449,7 +15631,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="C169">
         <v>704</v>
@@ -15532,7 +15714,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="C170">
         <v>658</v>
@@ -15615,7 +15797,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="C171">
         <v>883</v>
@@ -15698,7 +15880,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="C172">
         <v>748</v>
@@ -15781,7 +15963,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="C173">
         <v>891</v>
@@ -15864,7 +16046,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="C174">
         <v>1020</v>
@@ -15947,7 +16129,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="C175">
         <v>988</v>
@@ -16030,7 +16212,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="C176">
         <v>1029</v>
@@ -16113,7 +16295,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="C177">
         <v>1007</v>
@@ -16196,7 +16378,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="C178">
         <v>717</v>
@@ -16279,7 +16461,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C179">
         <v>766</v>
@@ -16362,7 +16544,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="C180">
         <v>890</v>
@@ -16445,7 +16627,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="C181">
         <v>1017</v>
@@ -16528,7 +16710,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="C182">
         <v>1167</v>
@@ -16611,7 +16793,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="C183">
         <v>574</v>
@@ -16694,7 +16876,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="C184">
         <v>681</v>
@@ -16777,7 +16959,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="C185">
         <v>622</v>
@@ -16860,7 +17042,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="C186">
         <v>961</v>
@@ -16943,7 +17125,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="C187">
         <v>833</v>
@@ -17026,7 +17208,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="C188">
         <v>957</v>
@@ -17109,7 +17291,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="C189">
         <v>803</v>
@@ -17192,7 +17374,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="C190">
         <v>586</v>
@@ -17275,7 +17457,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="C191">
         <v>733</v>
@@ -17358,7 +17540,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="C192">
         <v>959</v>
@@ -17441,7 +17623,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="C193">
         <v>969</v>
@@ -17524,7 +17706,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="C194">
         <v>617</v>
@@ -17607,7 +17789,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="C195">
         <v>1103</v>
@@ -17690,7 +17872,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="C196">
         <v>944</v>
@@ -17773,7 +17955,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C197">
         <v>657</v>
@@ -17856,7 +18038,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="C198">
         <v>745</v>
@@ -17939,7 +18121,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="C199">
         <v>822</v>
@@ -18022,7 +18204,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="C200">
         <v>878</v>
@@ -18105,7 +18287,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="C201">
         <v>865</v>
@@ -18188,7 +18370,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="C202">
         <v>756</v>
@@ -18271,7 +18453,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="C203">
         <v>1149</v>
@@ -18354,7 +18536,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="C204">
         <v>743</v>
@@ -18437,7 +18619,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="C205">
         <v>694</v>
@@ -18520,7 +18702,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="C206">
         <v>1091</v>
@@ -18603,7 +18785,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="C207">
         <v>762</v>
@@ -18686,7 +18868,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="C208">
         <v>672</v>
@@ -18769,7 +18951,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="C209">
         <v>714</v>
@@ -18852,7 +19034,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="C210">
         <v>1139</v>
@@ -18935,7 +19117,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="C211">
         <v>1011</v>
@@ -19018,7 +19200,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="C212">
         <v>715</v>
@@ -19101,7 +19283,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="C213">
         <v>1033</v>
@@ -19184,7 +19366,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="C214">
         <v>721</v>
@@ -19267,7 +19449,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="C215">
         <v>684</v>
@@ -19350,7 +19532,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="C216">
         <v>1054</v>
@@ -19433,7 +19615,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C217">
         <v>674</v>
@@ -19516,7 +19698,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C218">
         <v>682</v>
@@ -19599,7 +19781,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="C219">
         <v>729</v>
@@ -19682,7 +19864,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="C220">
         <v>1001</v>
@@ -19765,7 +19947,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="C221">
         <v>1085</v>
@@ -19848,7 +20030,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="C222">
         <v>809</v>
@@ -19931,7 +20113,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="C223">
         <v>589</v>
@@ -20014,7 +20196,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="C224">
         <v>661</v>
@@ -20097,7 +20279,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="C225">
         <v>796</v>
@@ -20180,7 +20362,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C226">
         <v>606</v>
@@ -20263,7 +20445,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="C227">
         <v>620</v>
@@ -20346,7 +20528,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="C228">
         <v>659</v>
@@ -20429,7 +20611,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="C229">
         <v>555</v>
@@ -20512,7 +20694,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="C230">
         <v>569</v>
@@ -20595,7 +20777,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="C231">
         <v>657</v>
@@ -20678,7 +20860,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="C232">
         <v>1028</v>
@@ -20761,7 +20943,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="C233">
         <v>504</v>
@@ -20844,7 +21026,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="C234">
         <v>805</v>
@@ -20927,7 +21109,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="C235">
         <v>865</v>
@@ -21010,7 +21192,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="C236">
         <v>1112</v>
@@ -21093,7 +21275,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="C237">
         <v>1002</v>
@@ -21176,7 +21358,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="C238">
         <v>573</v>
@@ -21259,7 +21441,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="C239">
         <v>848</v>
@@ -21342,7 +21524,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="C240">
         <v>793</v>
@@ -21425,7 +21607,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="C241">
         <v>838</v>
@@ -21508,7 +21690,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="C242">
         <v>854</v>
@@ -21591,7 +21773,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="C243">
         <v>909</v>
@@ -21674,7 +21856,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="C244">
         <v>451</v>
@@ -21757,7 +21939,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="C245">
         <v>782</v>
@@ -21840,7 +22022,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="C246">
         <v>1047</v>
@@ -21923,7 +22105,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="C247">
         <v>1020</v>
@@ -22006,7 +22188,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="C248">
         <v>748</v>
@@ -22089,7 +22271,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="C249">
         <v>739</v>
@@ -22172,7 +22354,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="C250">
         <v>885</v>
@@ -22255,7 +22437,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="C251">
         <v>677</v>
@@ -22338,7 +22520,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="C252">
         <v>688</v>
@@ -22421,7 +22603,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="C253">
         <v>1027</v>
@@ -22504,7 +22686,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="C254">
         <v>976</v>
@@ -22587,7 +22769,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="C255">
         <v>913</v>
@@ -22670,7 +22852,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="C256">
         <v>916</v>
@@ -22753,7 +22935,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="C257">
         <v>856</v>
@@ -22836,7 +23018,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C258">
         <v>1166</v>
@@ -22919,7 +23101,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="C259">
         <v>1172</v>
@@ -23002,7 +23184,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="C260">
         <v>1140</v>
@@ -23085,7 +23267,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="C261">
         <v>1136</v>
@@ -23168,7 +23350,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="C262">
         <v>766</v>
@@ -23251,7 +23433,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="C263">
         <v>725</v>
@@ -23334,7 +23516,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="C264">
         <v>1147</v>
@@ -23417,7 +23599,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="C265">
         <v>832</v>
@@ -23500,7 +23682,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="C266">
         <v>981</v>
@@ -23583,7 +23765,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="C267">
         <v>913</v>
@@ -23666,7 +23848,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="C268">
         <v>780</v>
@@ -23749,7 +23931,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="C269">
         <v>817</v>
@@ -23832,7 +24014,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="C270">
         <v>688</v>
@@ -23915,7 +24097,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="C271">
         <v>735</v>
@@ -23998,7 +24180,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="C272">
         <v>1088</v>
@@ -24081,7 +24263,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="C273">
         <v>885</v>
@@ -24164,7 +24346,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="C274">
         <v>678</v>
@@ -24247,7 +24429,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="C275">
         <v>1017</v>
@@ -24330,7 +24512,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="C276">
         <v>903</v>
@@ -24413,7 +24595,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="C277">
         <v>882</v>
@@ -24496,7 +24678,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="C278">
         <v>752</v>
@@ -24579,7 +24761,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="C279">
         <v>714</v>
@@ -24662,7 +24844,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="C280">
         <v>1034</v>
@@ -24745,7 +24927,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="C281">
         <v>667</v>
@@ -24828,7 +25010,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="C282">
         <v>648</v>
@@ -24911,7 +25093,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="C283">
         <v>713</v>
@@ -24994,7 +25176,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="C284">
         <v>847</v>
@@ -25077,7 +25259,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="C285">
         <v>829</v>
@@ -25160,7 +25342,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="C286">
         <v>680</v>
@@ -25243,7 +25425,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="C287">
         <v>955</v>
@@ -25326,7 +25508,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="C288">
         <v>701</v>
@@ -25409,7 +25591,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="C289">
         <v>664</v>
@@ -25492,7 +25674,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="C290">
         <v>710</v>
@@ -25575,7 +25757,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="C291">
         <v>1098</v>
@@ -25658,7 +25840,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="C292">
         <v>1168</v>
@@ -25741,7 +25923,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="C293">
         <v>771</v>
@@ -25824,7 +26006,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="C294">
         <v>1066</v>
@@ -25907,7 +26089,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="C295">
         <v>1061</v>
@@ -25990,7 +26172,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="C296">
         <v>994</v>
@@ -26073,7 +26255,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="C297">
         <v>975</v>
@@ -26156,7 +26338,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="C298">
         <v>1080</v>
@@ -26239,7 +26421,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="C299">
         <v>1071</v>
@@ -26322,7 +26504,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="C300">
         <v>1046</v>
@@ -26405,7 +26587,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="C301">
         <v>1047</v>
@@ -26488,7 +26670,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="C302">
         <v>962</v>
@@ -26571,7 +26753,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="C303">
         <v>767</v>
@@ -26654,7 +26836,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="C304">
         <v>871</v>
@@ -26737,7 +26919,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="C305">
         <v>1085</v>
@@ -26820,7 +27002,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="C306">
         <v>1103</v>
@@ -26903,7 +27085,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="C307">
         <v>673</v>
@@ -26986,7 +27168,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="C308">
         <v>859</v>
@@ -27069,7 +27251,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="C309">
         <v>868</v>
@@ -27152,7 +27334,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="C310">
         <v>1085</v>
@@ -27235,7 +27417,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="C311">
         <v>1016</v>
@@ -27318,7 +27500,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="C312">
         <v>925</v>
@@ -27401,7 +27583,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="C313">
         <v>646</v>
@@ -27484,7 +27666,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C314">
         <v>620</v>
@@ -27567,7 +27749,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="C315">
         <v>759</v>
@@ -27650,7 +27832,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="C316">
         <v>809</v>
@@ -27733,7 +27915,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="C317">
         <v>666</v>
@@ -27816,7 +27998,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="C318">
         <v>702</v>
@@ -27899,7 +28081,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="C319">
         <v>1084</v>
@@ -27982,7 +28164,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="C320">
         <v>841</v>
@@ -28065,7 +28247,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="C321">
         <v>374</v>
@@ -28148,7 +28330,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="C322">
         <v>1181</v>
@@ -28231,7 +28413,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="C323">
         <v>1019</v>
@@ -28314,7 +28496,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="C324">
         <v>737</v>
@@ -28397,7 +28579,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="C325">
         <v>797</v>
@@ -28480,7 +28662,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="C326">
         <v>1087</v>
@@ -28563,7 +28745,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="C327">
         <v>918</v>
@@ -28646,7 +28828,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="C328">
         <v>907</v>
@@ -28729,7 +28911,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="C329">
         <v>944</v>
@@ -28812,7 +28994,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="C330">
         <v>655</v>
@@ -28895,7 +29077,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="C331">
         <v>686</v>
@@ -28978,7 +29160,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="C332">
         <v>908</v>
@@ -29061,7 +29243,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="C333">
         <v>736</v>
@@ -29144,7 +29326,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="C334">
         <v>761</v>
@@ -29227,7 +29409,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="C335">
         <v>739</v>
@@ -29310,7 +29492,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="C336">
         <v>1017</v>
@@ -29393,7 +29575,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="C337">
         <v>846</v>
@@ -29476,7 +29658,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="C338">
         <v>759</v>
@@ -29559,7 +29741,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="C339">
         <v>759</v>
@@ -29642,7 +29824,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="C340">
         <v>500</v>
@@ -29725,7 +29907,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="C341">
         <v>1152</v>
@@ -29808,7 +29990,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="C342">
         <v>1148</v>
@@ -29891,7 +30073,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="C343">
         <v>1010</v>
@@ -29974,7 +30156,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="C344">
         <v>1021</v>
@@ -30057,7 +30239,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="C345">
         <v>1116</v>
@@ -30140,7 +30322,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="C346">
         <v>655</v>
@@ -30223,7 +30405,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="C347">
         <v>969</v>
@@ -30306,7 +30488,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="C348">
         <v>822</v>
@@ -30389,7 +30571,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="C349">
         <v>555</v>
@@ -30472,7 +30654,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="C350">
         <v>631</v>
@@ -30555,7 +30737,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="C351">
         <v>879</v>
@@ -30638,7 +30820,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="C352">
         <v>812</v>
@@ -30721,7 +30903,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="C353">
         <v>1129</v>
@@ -30804,7 +30986,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="C354">
         <v>1103</v>
@@ -30887,7 +31069,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="C355">
         <v>844</v>
@@ -30970,7 +31152,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="C356">
         <v>1111</v>
@@ -31053,7 +31235,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="C357">
         <v>1124</v>
@@ -31136,7 +31318,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="C358">
         <v>851</v>
@@ -31219,7 +31401,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="C359">
         <v>796</v>
@@ -31302,7 +31484,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="C360">
         <v>783</v>
@@ -31385,7 +31567,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="C361">
         <v>421</v>
@@ -31468,7 +31650,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="C362">
         <v>864</v>
@@ -31551,7 +31733,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="C363">
         <v>803</v>
@@ -31634,7 +31816,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="C364">
         <v>801</v>
@@ -31717,7 +31899,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="C365">
         <v>531</v>
@@ -31800,7 +31982,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="C366">
         <v>724</v>
@@ -31883,7 +32065,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="C367">
         <v>612</v>
@@ -31966,7 +32148,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="C368">
         <v>621</v>
@@ -32049,7 +32231,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="C369">
         <v>1040</v>
@@ -32132,7 +32314,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="C370">
         <v>709</v>
@@ -32215,7 +32397,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="C371">
         <v>820</v>
@@ -32298,7 +32480,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="C372">
         <v>800</v>
@@ -32381,7 +32563,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="C373">
         <v>820</v>
@@ -32464,7 +32646,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="C374">
         <v>903</v>
@@ -32547,7 +32729,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="C375">
         <v>836</v>
@@ -32630,7 +32812,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="C376">
         <v>779</v>
@@ -32713,7 +32895,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="C377">
         <v>904</v>
@@ -32796,7 +32978,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="C378">
         <v>884</v>
@@ -32879,7 +33061,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="C379">
         <v>839</v>
@@ -32962,7 +33144,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="C380">
         <v>742</v>
@@ -33045,7 +33227,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="C381">
         <v>864</v>
@@ -33128,7 +33310,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="C382">
         <v>846</v>
@@ -33211,7 +33393,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="C383">
         <v>767</v>
@@ -33294,7 +33476,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="C384">
         <v>1124</v>
@@ -33377,7 +33559,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="C385">
         <v>1038</v>
@@ -33460,7 +33642,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="C386">
         <v>964</v>
@@ -33543,7 +33725,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="C387">
         <v>784</v>
